--- a/backend/app/src/main/resources/templates/sales-order-import-template.xlsx
+++ b/backend/app/src/main/resources/templates/sales-order-import-template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="订单导入" sheetId="1" r:id="Rdb30055d1b9b4757"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R11eefbbac1544032"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="订单导入" sheetId="1" r:id="R8ddeee9492fa4409"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R5fd0511eb432481a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -733,9 +733,6 @@
       <x:c r="A5" s="16"/>
       <x:c r="B5" s="16"/>
       <x:c r="C5" s="18"/>
-      <x:c r="E5" t="str">
-        <x:v>正式订单</x:v>
-      </x:c>
       <x:c r="G5" s="16"/>
       <x:c r="H5" s="16"/>
       <x:c r="I5" s="25"/>
@@ -2392,7 +2389,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R611f4b25bb804006"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b1ba7540dd14ef4"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/backend/app/src/main/resources/templates/sales-order-import-template.xlsx
+++ b/backend/app/src/main/resources/templates/sales-order-import-template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="订单导入" sheetId="1" r:id="Radd5f9853c5b4094"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R7fd434fbde66422d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="订单导入" sheetId="1" r:id="Rf0304774a3504dc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="Rc5ffd56a202d45d3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -444,10 +444,10 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>DEMO-ORDER-001</x:v>
+        <x:v>SAMPLE-ORDER-001</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>DEMO-CUSTOMER-001</x:v>
+        <x:v>CUS000001</x:v>
       </x:c>
       <x:c r="C2" s="12" t="n">
         <x:v>46252</x:v>
@@ -459,60 +459,42 @@
         <x:v>正式订单</x:v>
       </x:c>
       <x:c r="F2" s="10" t="str">
-        <x:v>示例销售员</x:v>
+        <x:v>管理员</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>DEMO-PRODUCT-001</x:v>
+        <x:v>G_T5YZH60WPSC-M</x:v>
       </x:c>
       <x:c r="H2" s="11" t="str">
-        <x:v>DEMO-MATERIAL-001</x:v>
+        <x:v>G8T5VMHS02</x:v>
       </x:c>
       <x:c r="I2" s="15" t="n">
-        <x:v>2</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="J2" s="16" t="n">
-        <x:v>1280.5</x:v>
-      </x:c>
-      <x:c r="K2" s="10" t="str">
-        <x:v>示例业务联系人</x:v>
-      </x:c>
-      <x:c r="L2" s="11" t="str">
-        <x:v>13800000001</x:v>
-      </x:c>
-      <x:c r="M2" s="10" t="str">
-        <x:v>示例订单联系人</x:v>
-      </x:c>
-      <x:c r="N2" s="11" t="str">
-        <x:v>13800000002</x:v>
-      </x:c>
-      <x:c r="O2" s="10" t="str">
-        <x:v>示例财务联系人</x:v>
-      </x:c>
-      <x:c r="P2" s="11" t="str">
-        <x:v>13800000003</x:v>
-      </x:c>
-      <x:c r="Q2" s="10" t="str">
-        <x:v>示例省示例市示例区示例路 1 号</x:v>
-      </x:c>
-      <x:c r="R2" s="10" t="str">
-        <x:v>示例收货人</x:v>
-      </x:c>
-      <x:c r="S2" s="11" t="str">
-        <x:v>13800000004</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K2" s="10" t="str"/>
+      <x:c r="L2" s="11" t="str"/>
+      <x:c r="M2" s="10" t="str"/>
+      <x:c r="N2" s="11" t="str"/>
+      <x:c r="O2" s="10" t="str"/>
+      <x:c r="P2" s="11" t="str"/>
+      <x:c r="Q2" s="10" t="str"/>
+      <x:c r="R2" s="10" t="str"/>
+      <x:c r="S2" s="11" t="str"/>
       <x:c r="T2" s="10" t="str">
         <x:v>物流配送</x:v>
       </x:c>
       <x:c r="U2" s="10" t="str">
-        <x:v>占位示例：同一外部订单号的首条明细</x:v>
+        <x:v>数据库参考：同一外部订单号的首条明细</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="11" t="str">
-        <x:v>DEMO-ORDER-001</x:v>
+        <x:v>SAMPLE-ORDER-001</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>DEMO-CUSTOMER-001</x:v>
+        <x:v>CUS000001</x:v>
       </x:c>
       <x:c r="C3" s="12" t="n">
         <x:v>46252</x:v>
@@ -524,60 +506,42 @@
         <x:v>正式订单</x:v>
       </x:c>
       <x:c r="F3" s="10" t="str">
-        <x:v>示例销售员</x:v>
+        <x:v>管理员</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>DEMO-PRODUCT-002</x:v>
+        <x:v>BR_A71YZH60WPSE</x:v>
       </x:c>
       <x:c r="H3" s="11" t="str">
-        <x:v>DEMO-MATERIAL-002</x:v>
+        <x:v>G8A71HS001</x:v>
       </x:c>
       <x:c r="I3" s="15" t="n">
-        <x:v>5</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="J3" s="16" t="n">
-        <x:v>860</x:v>
-      </x:c>
-      <x:c r="K3" s="10" t="str">
-        <x:v>示例业务联系人</x:v>
-      </x:c>
-      <x:c r="L3" s="11" t="str">
-        <x:v>13800000001</x:v>
-      </x:c>
-      <x:c r="M3" s="10" t="str">
-        <x:v>示例订单联系人</x:v>
-      </x:c>
-      <x:c r="N3" s="11" t="str">
-        <x:v>13800000002</x:v>
-      </x:c>
-      <x:c r="O3" s="10" t="str">
-        <x:v>示例财务联系人</x:v>
-      </x:c>
-      <x:c r="P3" s="11" t="str">
-        <x:v>13800000003</x:v>
-      </x:c>
-      <x:c r="Q3" s="10" t="str">
-        <x:v>示例省示例市示例区示例路 1 号</x:v>
-      </x:c>
-      <x:c r="R3" s="10" t="str">
-        <x:v>示例收货人</x:v>
-      </x:c>
-      <x:c r="S3" s="11" t="str">
-        <x:v>13800000004</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K3" s="10" t="str"/>
+      <x:c r="L3" s="11" t="str"/>
+      <x:c r="M3" s="10" t="str"/>
+      <x:c r="N3" s="11" t="str"/>
+      <x:c r="O3" s="10" t="str"/>
+      <x:c r="P3" s="11" t="str"/>
+      <x:c r="Q3" s="10" t="str"/>
+      <x:c r="R3" s="10" t="str"/>
+      <x:c r="S3" s="11" t="str"/>
       <x:c r="T3" s="10" t="str">
         <x:v>物流配送</x:v>
       </x:c>
       <x:c r="U3" s="10" t="str">
-        <x:v>占位示例：同一外部订单号的第二条明细</x:v>
+        <x:v>数据库参考：同一外部订单号的第二条明细</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="28" customHeight="1">
       <x:c r="A4" s="11" t="str">
-        <x:v>DEMO-ORDER-002</x:v>
+        <x:v>SAMPLE-ORDER-002</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>DEMO-CUSTOMER-002</x:v>
+        <x:v>CUS000002</x:v>
       </x:c>
       <x:c r="C4" s="12" t="n">
         <x:v>46253</x:v>
@@ -589,52 +553,34 @@
         <x:v>草稿</x:v>
       </x:c>
       <x:c r="F4" s="10" t="str">
-        <x:v>示例销售员</x:v>
+        <x:v>管理员</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>DEMO-PRODUCT-003</x:v>
+        <x:v>G_T7PBY10WPSC-P</x:v>
       </x:c>
       <x:c r="H4" s="11" t="str">
-        <x:v>DEMO-MATERIAL-003</x:v>
+        <x:v>G8T7VPYS01</x:v>
       </x:c>
       <x:c r="I4" s="15" t="n">
-        <x:v>1</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="J4" s="16" t="n">
-        <x:v>399.99</x:v>
-      </x:c>
-      <x:c r="K4" s="10" t="str">
-        <x:v>示例业务联系人</x:v>
-      </x:c>
-      <x:c r="L4" s="11" t="str">
-        <x:v>13800000011</x:v>
-      </x:c>
-      <x:c r="M4" s="10" t="str">
-        <x:v>示例订单联系人</x:v>
-      </x:c>
-      <x:c r="N4" s="11" t="str">
-        <x:v>13800000012</x:v>
-      </x:c>
-      <x:c r="O4" s="10" t="str">
-        <x:v>示例财务联系人</x:v>
-      </x:c>
-      <x:c r="P4" s="11" t="str">
-        <x:v>13800000013</x:v>
-      </x:c>
-      <x:c r="Q4" s="10" t="str">
-        <x:v>示例省示例市示例区示例路 2 号</x:v>
-      </x:c>
-      <x:c r="R4" s="10" t="str">
-        <x:v>示例收货人</x:v>
-      </x:c>
-      <x:c r="S4" s="11" t="str">
-        <x:v>13800000014</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K4" s="10" t="str"/>
+      <x:c r="L4" s="11" t="str"/>
+      <x:c r="M4" s="10" t="str"/>
+      <x:c r="N4" s="11" t="str"/>
+      <x:c r="O4" s="10" t="str"/>
+      <x:c r="P4" s="11" t="str"/>
+      <x:c r="Q4" s="10" t="str"/>
+      <x:c r="R4" s="10" t="str"/>
+      <x:c r="S4" s="11" t="str"/>
       <x:c r="T4" s="10" t="str">
         <x:v>客户自提</x:v>
       </x:c>
       <x:c r="U4" s="10" t="str">
-        <x:v>占位示例：草稿订单不锁定库存</x:v>
+        <x:v>数据库参考：草稿订单不锁定库存</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2879,7 +2825,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58ce97b039a14e35"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0e00ffea0d845d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2941,7 +2887,7 @@
         <x:v>同一外部订单号的客户编码、订单日期、订单类型、销售员、订单状态、联系人、收货信息、发货方式和备注必须一致。</x:v>
       </x:c>
       <x:c r="D4" s="22" t="str">
-        <x:v>DEMO-ORDER-001 的两行应填写相同订单级字段</x:v>
+        <x:v>SAMPLE-ORDER-001 的两行应填写相同订单级字段</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="36" hidden="0" customHeight="1">
@@ -2955,7 +2901,7 @@
         <x:v>客户编码必须唯一匹配一个已启用客户。</x:v>
       </x:c>
       <x:c r="D5" s="22" t="str">
-        <x:v>DEMO-CUSTOMER-001 仅为占位示例</x:v>
+        <x:v>CUS000001 取自本地开发数据库，仅供参考</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="36" hidden="0" customHeight="1">
@@ -2969,7 +2915,7 @@
         <x:v>产品编号必须唯一匹配一个已启用产品；同一订单可填写多个不同产品。</x:v>
       </x:c>
       <x:c r="D6" s="22" t="str">
-        <x:v>DEMO-PRODUCT-001 仅为占位示例</x:v>
+        <x:v>G_T5YZH60WPSC-M 取自本地开发数据库，仅供参考</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="36" hidden="0" customHeight="1">
@@ -3050,7 +2996,7 @@
         <x:v>必须替换</x:v>
       </x:c>
       <x:c r="C12" s="22" t="str">
-        <x:v>模板内所有 DEMO 编码和示例联系人均为格式占位，不代表系统真实数据。</x:v>
+        <x:v>客户编码、产品编号、客户料号和销售员取自本地开发数据库；外部订单号和日期仅为示例。</x:v>
       </x:c>
       <x:c r="D12" s="22" t="str">
         <x:v>导入前请替换全部示例值</x:v>
